--- a/tests/fixtures/legal/hidden.xlsx
+++ b/tests/fixtures/legal/hidden.xlsx
@@ -21,7 +21,7 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/persons/person1.xml><?xml version="1.0" encoding="utf-8"?>
 <persons xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
   <person/>
 </persons>
